--- a/evaluation/fairness_measure_based/OLS_Regression_Feature_Analysis_Overestimation_Unfairness_of_sensitive_attribute.xlsx
+++ b/evaluation/fairness_measure_based/OLS_Regression_Feature_Analysis_Overestimation_Unfairness_of_sensitive_attribute.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,28 +441,78 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>P-Value</t>
+          <t>t</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Significance</t>
+          <t>P-Value (raw)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P-Value (Bonferroni)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Reject (Bonf@0.05)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Partial_R2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cohen_f2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Significance (raw)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Significance (bonf)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mean Rating</t>
+          <t>Rating per User</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2809595208400512</v>
+        <v>0.1543708092456756</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0009318548734194018</v>
-      </c>
-      <c r="D2" t="inlineStr">
+        <v>12.56244683850065</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.067497726502384e-33</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4.548494998305244e-32</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1520647319984036</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.040649621199604</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>***</t>
         </is>
@@ -471,16 +521,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rating per User</t>
+          <t>Number of Users</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1503339900643861</v>
+        <v>0.148978005590138</v>
       </c>
       <c r="C3" t="n">
-        <v>6.143361610142753e-21</v>
-      </c>
-      <c r="D3" t="inlineStr">
+        <v>7.022039047830735</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.372353929589953e-12</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9.619178645097896e-11</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.05305988715345394</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.3631134632040467</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>***</t>
         </is>
@@ -489,16 +559,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Number of Users</t>
+          <t>Gini User</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1339370886492275</v>
+        <v>0.1210362599382468</v>
       </c>
       <c r="C4" t="n">
-        <v>2.593142508687494e-07</v>
-      </c>
-      <c r="D4" t="inlineStr">
+        <v>6.640011101659173</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.483852802460551e-11</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.206447616541321e-09</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0477115426859439</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.326512256790072</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>***</t>
         </is>
@@ -507,16 +597,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gini User</t>
+          <t>Number of Ratings</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1198282330993105</v>
+        <v>-0.1658755883865336</v>
       </c>
       <c r="C5" t="n">
-        <v>9.232404203616297e-08</v>
-      </c>
-      <c r="D5" t="inlineStr">
+        <v>-5.290522114393715</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.540294688654439e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.388648315039766e-06</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.03082592960930319</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2109561602448606</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>***</t>
         </is>
@@ -525,16 +635,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of Items</t>
+          <t>Mean Rating</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1040893371548686</v>
+        <v>0.3566229284915785</v>
       </c>
       <c r="C6" t="n">
-        <v>3.137322534301756e-06</v>
-      </c>
-      <c r="D6" t="inlineStr">
+        <v>5.100270877781096</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.154539329505786e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9.139986524912728e-06</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0287112545079833</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1964844558974523</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>***</t>
         </is>
@@ -543,18 +673,38 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gini Item</t>
+          <t>Number of Items</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.06811361491630952</v>
+        <v>0.07794386401236721</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03890783117430289</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>*</t>
+        <v>4.274580404837748</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.12408353921869e-05</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0004672983786281118</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.02034131852248322</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.1392050946786587</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>***</t>
         </is>
       </c>
     </row>
@@ -565,12 +715,32 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05095606694247632</v>
+        <v>0.03483916334042636</v>
       </c>
       <c r="C8" t="n">
-        <v>4.938469552821116e-15</v>
-      </c>
-      <c r="D8" t="inlineStr">
+        <v>4.238704465620038</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.485530110539469e-05</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0005468166243186831</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.02000811080924815</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1369247994648908</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>***</t>
         </is>
@@ -579,208 +749,488 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Standart Deviation of Rating</t>
+          <t>Shape</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04952294379931693</v>
+        <v>-0.07085697827066822</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2670638963708146</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>-3.473350133891423</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0005390704816672743</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01185955059668004</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01352387157557805</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.09255013734825196</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dataset_BX</t>
+          <t>Gini Item</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04818394101441462</v>
+        <v>0.04598340662077555</v>
       </c>
       <c r="C10" t="n">
-        <v>0.197913365641521</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+        <v>1.672723603586356</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0947371592810982</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.003169472790504742</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.02169017506883737</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Density</t>
+          <t>Skewness of Long Tail Items</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02938939754241546</v>
+        <v>-0.01833247103554086</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3543263937215796</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
+        <v>-1.479946347307419</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1392454631375796</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.002482731148728043</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01699048290494747</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Skewness of Popularity Bias</t>
+          <t>Model Name_NFCF</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01610090106588837</v>
+        <v>30641407569.01118</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2877783741579483</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+        <v>0.9642776961804249</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.3351716237549737</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.001055511395037875</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.007223354942220008</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Rating per Item</t>
+          <t>Dataset_BX</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01311201678266867</v>
+        <v>45696011154.2886</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6250230895703482</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+        <v>0.9642776961800803</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.3351716237551459</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.001055511395037121</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.007223354942214851</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Skewness of Long Tail Items</t>
+          <t>Sensitive Feature_Gender</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.01665518640708223</v>
+        <v>-151717365474.6238</v>
       </c>
       <c r="C14" t="n">
-        <v>0.263667599191738</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
+        <v>-0.9642776961786708</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.3351716237558523</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.001055511395034039</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.007223354942193756</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Difference between Sensitive Attribute Percentage</t>
+          <t>Sensitive Feature_Age</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.02143231889816992</v>
+        <v>-151717365474.6187</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5121331404872325</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
+        <v>-0.9642776961786391</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.3351716237558678</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.00105551139503397</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.007223354942193282</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sensitive Feature_Age</t>
+          <t>Model Name_PFCN_MLP</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.04310289071592132</v>
+        <v>30641407568.94719</v>
       </c>
       <c r="C16" t="n">
-        <v>0.003935266002851822</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>**</t>
-        </is>
-      </c>
+        <v>0.9642776961784104</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.3351716237559826</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.00105551139503347</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.00722335494218986</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sensitive Feature_Gender</t>
+          <t>const</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.04464267559254911</v>
+        <v>75379946751.35321</v>
       </c>
       <c r="C17" t="n">
-        <v>0.001231119301361929</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>**</t>
-        </is>
-      </c>
+        <v>0.9642776961774513</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.3351716237564629</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.001055511395031372</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.007223354942175505</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Shape</t>
+          <t>Dataset_ml1m</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.06016384421724617</v>
+        <v>45696011154.05704</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01460936924054813</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
+        <v>0.9642776961751607</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.3351716237576106</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.001055511395026363</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.007223354942141224</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>const</t>
+          <t>Model Name_FOCF</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.08774556630847027</v>
+        <v>30641407568.80829</v>
       </c>
       <c r="C19" t="n">
-        <v>0.001609714450238563</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>**</t>
-        </is>
-      </c>
+        <v>0.9642776961740348</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.3351716237581744</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.0010555113950239</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.007223354942124374</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dataset_ml1m</t>
+          <t>Skewness of Popularity Bias</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1359295073228849</v>
+        <v>0.01211186835689744</v>
       </c>
       <c r="C20" t="n">
-        <v>0.01162285091048564</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
+        <v>0.9521238693609491</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.3412956006114056</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.001029098799457496</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.007042601277485254</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Number of Ratings</t>
+          <t>Difference between Sensitive Attribute Percentage</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.143864936775756</v>
+        <v>-0.02331394357689807</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0001597925209954752</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>***</t>
-        </is>
-      </c>
+        <v>-0.8566487729805893</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.3918722328884459</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0008332223436724068</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.005702127672357578</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Rating per Item</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.01669495574443184</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.7474841231819451</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.4549710679346063</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.0006345204400093079</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.004342318214495812</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Density</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.01706642642713729</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.6522918868965573</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.5143832342066351</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.0004832716829559887</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.003307252689005655</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Standart Deviation of Rating</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-0.02374716924613215</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.6405019415231727</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.5220130676827623</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.0004659677013974258</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.003188833502534774</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
